--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/ALABAMA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/ALABAMA_2012.xlsx
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C130">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C152">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C531">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C589">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C605">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C854">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C961">
